--- a/data/review_matches.xlsx
+++ b/data/review_matches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,554 +456,554 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10kg-yoggies-kureci-hovezi-maso-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>5-1-yoggies-jeleni-konzerva-s-pohankou-a-brusinkami-800g</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10 kg Yoggies Kuřecí &amp; hovězí maso, granule lisované za studena s probiotiky</t>
+          <t>5+1 Yoggies hert blikvoer met boekweit en veenbessen 800 g</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
+          <t>Yoggies blik hert met boekweit en veenbessen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
+          <t>https://doglife.be/product/400g-yoggies-blikhertenvlees-met-boekweit-en-veenbessen</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33,20</t>
+          <t>3,30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.699</v>
+        <v>0.698</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20kg-kureci-a-hovezi-maso-granule-lisovane-za-studena-yoggies</t>
+          <t>5-1-yoggies-jeleni-konzerva-s-pohankou-a-brusinkami-400g</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20 kg Yoggies Kuřecí &amp; hovězí maso, granule lisované za studena s probiotiky</t>
+          <t>5+1 Yoggies hert blikvoer met boekweit en veenbessen 400 g</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
+          <t>Yoggies blik hert met boekweit en veenbessen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
+          <t>https://doglife.be/product/400g-yoggies-blikhertenvlees-met-boekweit-en-veenbessen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33,20</t>
+          <t>3,30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.699</v>
+        <v>0.698</v>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2kg-kureci-a-hovezi-maso-granule-lisovane-za-studena-s-probiotiky-yoggies</t>
+          <t>800g-yoggies-jeleni-konzerva-s-pohankou-a-brusinkami</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2 kg Yoggies Kuřecí &amp; hovězí maso, granule lisované za studena s probiotiky</t>
+          <t>800 g Yoggies hert blikvoer met boekweit en veenbessen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
+          <t>Yoggies blik hert met boekweit en veenbessen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
+          <t>https://doglife.be/product/400g-yoggies-blikhertenvlees-met-boekweit-en-veenbessen</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33,20</t>
+          <t>3,30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.699</v>
+        <v>0.698</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5-kg-kureci-a-hovezi-maso-granule-lisovane-za-studena-s-probiotiky-yoggies</t>
+          <t>400g-yoggies-jeleni-konzerva-s-pohankou-a-brusinkami</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5 kg Yoggies Kuřecí &amp; hovězí maso, granule lisované za studena s probiotiky</t>
+          <t>400 g Yoggies hert blikvoer met boekweit en veenbessen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
+          <t>Yoggies blik hert met boekweit en veenbessen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
+          <t>https://doglife.be/product/400g-yoggies-blikhertenvlees-met-boekweit-en-veenbessen</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33,20</t>
+          <t>3,30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.699</v>
+        <v>0.698</v>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15kg-kureci-a-hovezi-maso-granule-lisovane-za-studena-yoggies</t>
+          <t>yoggies-ragu-pro-kocky-losos-a-kachna-24-x-185-zvyhodnene-baleni</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15 kg Yoggies Kuřecí &amp; hovězí maso, granule lisované za studena s probiotiky</t>
+          <t>Yoggies RAGÚ voor katten, zalm en eend 24 x 185 - voordeelverpakking</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
+          <t>185g Yoggies RAGOUT voor katten Kalkoen &amp; Zalm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
+          <t>https://doglife.be/product/185g-yoggies-ragout-voor-katten-kalkoen-zalm</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33,20</t>
+          <t>3,20</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.699</v>
+        <v>0.697</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>yoggies-ragu-pro-kocky-losos-a-kachna-24-x-185-zvyhodnene-baleni</t>
+          <t>2kg-yoggies-vet-veggie-bez-masa-granule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yoggies RAGÚ pro kočky, losos a kachna 24 x 185 - zvýhodněné balení</t>
+          <t>2 kg Yoggies VET Veggie vleesvrij, koudgeperste brokken met probiotica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>185g Yoggies RAGOUT voor katten Kalkoen &amp; Zalm</t>
+          <t>2 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste  MINI korrels met probiotica</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/185g-yoggies-ragout-voor-katten-kalkoen-zalm</t>
+          <t>https://doglife.be/product/2-kg-yoggies-vet-gastro-sensitive-met-kalkoenvlees-koudgeperste-mini-korrels-met-probiotica</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3,20</t>
+          <t>19,70</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.697</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2kg-yoggies-vet-gastro-sensitive-s-krutim-masem-minigranule-lisovane-za-studena-s-probiotiky</t>
+          <t>10kg-yoggies-active-kachni-maso-zverina-minigranule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2 kg Yoggies VET Gastro Sensitive s krůtím masem, MINIgranule lisované za studena s probiotiky</t>
+          <t>10 kg Yoggies Active eendenvlees &amp; wild, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste  MINI korrels met probiotica</t>
+          <t>Yoggies ACTIVE vlees van wild</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/2-kg-yoggies-vet-gastro-sensitive-met-kalkoenvlees-koudgeperste-mini-korrels-met-probiotica</t>
+          <t>https://doglife.be/product/yoggies-active-vlees-van-wild</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19,70</t>
+          <t>2,70</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.658</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5-1-yoggies-hovezi-konzerva-s-ostropestrcem-marianskym-400g</t>
+          <t>2-kg-minigranule-yoggies-active-kachna-a-zverina-granule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5+1 Yoggies hovězí konzerva s ostropestřcem mariánským 400 g</t>
+          <t>2 kg Yoggies Active eendenvlees &amp; wild, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>400g Yoggies blik rundvlees met mariadistel</t>
+          <t>Yoggies ACTIVE vlees van wild</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-monoproteine-rund-met-mariadistel-400g</t>
+          <t>https://doglife.be/product/yoggies-active-vlees-van-wild</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3,30</t>
+          <t>2,70</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.658</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>400g-yoggies-hovezi-konzerva-s-ostropestrcem-marianskym</t>
+          <t>5-kg-minigranule-yoggies-active-kachna-a-zverina-granule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>400 g Yoggies hovězí konzerva s ostropestřcem mariánským</t>
+          <t>5 kg Yoggies Active eendenvlees &amp; wild, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>400g Yoggies blik rundvlees met mariadistel</t>
+          <t>Yoggies ACTIVE vlees van wild</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-monoproteine-rund-met-mariadistel-400g</t>
+          <t>https://doglife.be/product/yoggies-active-vlees-van-wild</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3,30</t>
+          <t>2,70</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.658</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2kg-yoggies-vet-insect-derma-s-hmyzim-proteinem-minigranule-lisovane-za-studena-s-probiotiky</t>
+          <t>15kg-minigranule-yoggies-active-kachna-a-zverina-granule-lisovane-za-studena</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2 kg Yoggies VET Insect Derma s hmyzím proteinem, MINIgranule lisované za studena s probiotiky</t>
+          <t>15 kg Yoggies Active eendenvlees &amp; wild, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2 kg Yoggies VET Insect Derma met insectenproteïne, koudgeperste MINI korrels met probiotica</t>
+          <t>Yoggies ACTIVE vlees van wild</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/2-kg-yoggies-vet-insect-derma-met-insectenproteine-koudgeperste-mini-korrels-met-probiotica</t>
+          <t>https://doglife.be/product/yoggies-active-vlees-van-wild</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18,90</t>
+          <t>2,70</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.671</v>
+        <v>0.658</v>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10kg-yoggies-active-kachni-maso-zverina-minigranule-lisovane-za-studena-s-probiotiky</t>
+          <t>yoggies-barf-za-studena-lisovana-priloha-k-syrovemu-masu-s-probiotiky</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10 kg Yoggies Active Kachní maso &amp; zvěřina, MINIgranule lisované za studena s probiotiky</t>
+          <t>Yoggies BARF+ koudgeperst bijgerecht bij rauw vlees met probiotica</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yoggies ACTIVE vlees van wild</t>
+          <t>Yoggies BARF+ bijgerecht voor rauw vlees, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-active-vlees-van-wild</t>
+          <t>https://doglife.be/product/barf-volledig-vleesloos-gerecht-aan-b-a-r-f</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2,70</t>
+          <t>14,40</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.658</v>
+        <v>0.657</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2-kg-minigranule-yoggies-active-kachna-a-zverina-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>5-1-yoggies-drubezi-konzerva-se-zeleninou-a-ovesnymi-vlockami-200g</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2 kg Yoggies Active Kachní maso &amp; zvěřina, MINIgranule lisované za studena s probiotiky</t>
+          <t>5+1 Yoggies gevogelte blikvoer met groenten en havervlokken 200 g</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yoggies ACTIVE vlees van wild</t>
+          <t>200g Yoggies blik gevogelte met groenten en havermout</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-active-vlees-van-wild</t>
+          <t>https://doglife.be/product/yoggies-blik-gevogelte-met-havermout-en-groenten-200-g</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2,70</t>
+          <t>1,60</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.658</v>
+        <v>0.65</v>
       </c>
       <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5-kg-minigranule-yoggies-active-kachna-a-zverina-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>200g-yoggies-drubezi-konzerva-s-ovesnymi-vlockami</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5 kg Yoggies Active Kachní maso &amp; zvěřina, MINIgranule lisované za studena s probiotiky</t>
+          <t>200 g Yoggies gevogelte blikvoer met groenten en havervlokken</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yoggies ACTIVE vlees van wild</t>
+          <t>200g Yoggies blik gevogelte met groenten en havermout</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-active-vlees-van-wild</t>
+          <t>https://doglife.be/product/yoggies-blik-gevogelte-met-havermout-en-groenten-200-g</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2,70</t>
+          <t>1,60</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.658</v>
+        <v>0.65</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15kg-minigranule-yoggies-active-kachna-a-zverina-granule-lisovane-za-studena</t>
+          <t>tabletky-luposan-biotin-pro-psy-i-kocky-na-zdrave-drapy-srst-i-kuzi-180g-200ks</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15 kg Yoggies Active Kachní maso &amp; zvěřina, MINIgranule lisované za studena s probiotiky</t>
+          <t>Luposan Biotin+ tabletten voor honden en katten voor gezonde nagels, vacht en huid, 180 g/200 st.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yoggies ACTIVE vlees van wild</t>
+          <t>LUPO BIOTIN tabletten (huid,vacht en klauwen)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-active-vlees-van-wild</t>
+          <t>https://doglife.be/product/lupo-biotin-tabletten</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2,70</t>
+          <t>21,00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.658</v>
+        <v>0.648</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>700g-b-a-r-f-hovezi-maso-s-krutou-a-s-probiotiky</t>
+          <t>10kg-yoggies-kruti-maso-jahly-minigranule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>700 g BARF Hovězí maso s krůtou a s probiotiky</t>
+          <t>10 kg Yoggies kalkoenvlees &amp; gierst, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>700 g Yoggies BARF 100% rundvlees met probiotica Rauw vlees voor honden</t>
+          <t>Yoggies Kalkoen met Gierst, koudgeperste korrels met probiotica Klassiek</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/700-g-yoggies-barf-100-rundvlees-met-probiotica-rauw-vlees-voor-honden</t>
+          <t>https://doglife.be/product/hypoalergeen-kalkoenvlees-met-gierst-en-hennepolie-klassiek</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>36,40</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.654</v>
+        <v>0.643</v>
       </c>
       <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5-1-yoggies-kozi-konzerva-s-bramborem-a-mrkvi-800g</t>
+          <t>15-kg-minigranule-monoproteinove-yoggies-s-krutim-masem-a-jahly-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5+1 Yoggies kozí konzerva s bramborem a mrkví 800 g</t>
+          <t>15 kg Yoggies kalkoenvlees &amp; gierst, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>800g Yoggies blik geit met aardappelen en wortelen</t>
+          <t>Yoggies Kalkoen met Gierst, koudgeperste korrels met probiotica Klassiek</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-geit-met-aardappelen-en-wortelen-800-g</t>
+          <t>https://doglife.be/product/hypoalergeen-kalkoenvlees-met-gierst-en-hennepolie-klassiek</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5,30</t>
+          <t>36,40</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.644</v>
+        <v>0.643</v>
       </c>
       <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>800g-yoggies-kozi-konzerva-s-bramborem-a-mrkvi</t>
+          <t>5-kg-minigranule-monoproteinove-yoggies-s-krutim-masem-a-jahly-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>800 g Yoggies kozí konzerva s bramborem a mrkví</t>
+          <t>5 kg Yoggies kalkoenvlees &amp; gierst, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>800g Yoggies blik geit met aardappelen en wortelen</t>
+          <t>Yoggies Kalkoen met Gierst, koudgeperste korrels met probiotica Klassiek</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-geit-met-aardappelen-en-wortelen-800-g</t>
+          <t>https://doglife.be/product/hypoalergeen-kalkoenvlees-met-gierst-en-hennepolie-klassiek</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5,30</t>
+          <t>36,40</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.644</v>
+        <v>0.643</v>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>650g-yoggies-varena-potrava-pro-psy-veprove-maso-s-ryzi</t>
+          <t>2kg-minigranule-monoproteinove-yoggies-s-krutim-masem-a-jahly-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>650 g Yoggies Vařená potrava pro psy – vepřové maso s rýží</t>
+          <t>2 kg Yoggies kalkoenvlees &amp; gierst, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>650g Yoggies Gekookt Hondenvoer – Varken met Rijst</t>
+          <t>Yoggies Kalkoen met Gierst, koudgeperste korrels met probiotica Klassiek</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-650g-gekookt-hondenvoer-varkensvlees-met-rijst</t>
+          <t>https://doglife.be/product/hypoalergeen-kalkoenvlees-met-gierst-en-hennepolie-klassiek</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6,90</t>
+          <t>36,40</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1014,384 +1014,384 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1-5kg-yoggies-b-a-r-f-pro-kocky-100-kruti-komplet-s-pivovar-kvasnicemi-a-konopnym-olejem-s-probiotiky</t>
+          <t>sodapup-lizaci-podlozka-puzzle-20-x-20cm-zelena</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6x250 g Yoggies BARF pro kočky 100% Krůtí komplet s pivovar. kvasnicemi a konopným olejem s probiotiky</t>
+          <t>SodaPup likmat puzzel, groen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1,5 kg (6x250gr)Yoggies BARF 100% Kalkoen, compleet met biergist en hennepolie met probiotica Rauw voedsel voor katten</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/6x250-gr-b-a-r-f-100-kalkoen-compleet</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17,20</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.634</v>
+        <v>0.642</v>
       </c>
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>yoggies-panske-triko-basic-lime-vel-xl</t>
+          <t>5-1-yoggies-drubezi-konzerva-se-zeleninou-a-ovesnymi-vlockami-400g</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yoggies pánské triko Basic lime vel. XL</t>
+          <t>5+1 Yoggies gevogelte blikvoer met groenten en havervlokken 400 g</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cat Basic</t>
+          <t>LIZA 400g gevogelte</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-catbasic-koudgeperste-korrels</t>
+          <t>https://doglife.be/product/liza-400g-gevogelte</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9,50</t>
+          <t>2,00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.629</v>
+        <v>0.639</v>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>yoggies-panske-triko-basic-lime-vel-l</t>
+          <t>400g-yoggies-drubezi-konzerva-se-zeleninou-a-ovesnymi-vlockami</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yoggies pánské triko Basic lime vel. L</t>
+          <t>400 g Yoggies gevogelte blikvoer met groenten en havervlokken</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cat Basic</t>
+          <t>LIZA 400g gevogelte</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-catbasic-koudgeperste-korrels</t>
+          <t>https://doglife.be/product/liza-400g-gevogelte</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9,50</t>
+          <t>2,00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.629</v>
+        <v>0.639</v>
       </c>
       <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5kg-yoggies-vet-veggie-bez-masa-minigranule-lisovane-za-studena-s-probiotiky</t>
+          <t>yoggies-konzerva-hovezi-s-ostropestrcem-marianskym</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5 kg Yoggies VET Veggie bez masa, MINIgranule lisované za studena s probiotiky</t>
+          <t>Yoggies blikvoer rund met mariadistel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5 kg Yoggies VET Veggie zonder vlees, koudgeperste korrels met probiotica</t>
+          <t>400g Yoggies blik rundvlees met mariadistel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/vet-veggie-zonder-vlees-met-probiotica-5kg</t>
+          <t>https://doglife.be/product/yoggies-monoproteine-rund-met-mariadistel-400g</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34,00</t>
+          <t>3,30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.628</v>
+        <v>0.629</v>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yoggies-jogurt-pro-psy-a-kocky-150g-1</t>
+          <t>yoggies-panske-triko-basic-lime-vel-xl</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Yoggies jogurt pro psy a kočky 150 g</t>
+          <t>Yoggies herenshirt Basic lime mt. XL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yoggies Polyfenolen (poeder van blauwe druivenpitten)voor honden en katten 150g</t>
+          <t>Cat Basic</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/polyfenolen-poeder-zaden-van-blauwe-druivensoorten</t>
+          <t>https://doglife.be/product/yoggies-catbasic-koudgeperste-korrels</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9,10</t>
+          <t>9,50</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.627</v>
+        <v>0.629</v>
       </c>
       <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>yoggies-jogurt-pro-psy-a-kocky-150g</t>
+          <t>yoggies-panske-triko-basic-lime-vel-l</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yoggies jogurt pro psy a kočky, 150 g</t>
+          <t>Yoggies herenshirt Basic lime mt. L</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yoggies Polyfenolen (poeder van blauwe druivenpitten)voor honden en katten 150g</t>
+          <t>Cat Basic</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/polyfenolen-poeder-zaden-van-blauwe-druivensoorten</t>
+          <t>https://doglife.be/product/yoggies-catbasic-koudgeperste-korrels</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9,10</t>
+          <t>9,50</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.627</v>
+        <v>0.629</v>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>degustacni-menu-5-1-zdarma-6x-150g-yoggies-varena-potrava-pro-psy</t>
+          <t>sodapup-mandala-nylonova-senzoricka-miska-modra</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Degustační menu 5+1 zdarma (6x150 g) Yoggies Vařená potrava pro psy</t>
+          <t>SodaPup Mandala, sensorische kom van nylon – blauw</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6x150g Yoggies yoghurt voor honden en katten</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoghurt-yoggies-6-x-150-g</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12,60</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.624</v>
+        <v>0.628</v>
       </c>
       <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5-1-yoggies-kachni-konzerva-s-hruskou-a-jahlami-400g</t>
+          <t>yoggies-jogurt-pro-psy-a-kocky-150g-1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5+1 Yoggies kachní konzerva s hruškou a jáhlami 400 g</t>
+          <t>Yoggies yoghurt voor honden en katten 150 g</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LIZA 400g Eend</t>
+          <t>Yoggies Polyfenolen (poeder van blauwe druivenpitten)voor honden en katten 150g</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/liza-400g-eend</t>
+          <t>https://doglife.be/product/polyfenolen-poeder-zaden-van-blauwe-druivensoorten</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2,00</t>
+          <t>9,10</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.622</v>
+        <v>0.627</v>
       </c>
       <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5-1-yoggies-kachni-konzerva-s-hruskou-a-jahlami-800g</t>
+          <t>sodapup-mandala-nylonova-senzoricka-miska-zluta</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5+1 Yoggies kachní konzerva s hruškou a jáhlami 800 g</t>
+          <t>SodaPup Mandala, sensorische kom van nylon - geel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LIZA 800g Eend</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/liza-800g-eend</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3,60</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.622</v>
+        <v>0.617</v>
       </c>
       <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>800g-yoggies-kachni-konzerva-s-hruskou-a-jahlami</t>
+          <t>yoggies-ekologicke-stelivo-pro-kocky-3kg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>800 g Yoggies kachní konzerva s hruškou a jáhlami</t>
+          <t>Yoggies ecologische kattenbakvulling 3 kg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LIZA 800g Eend</t>
+          <t>Yoggies – Ecologisch kattenbakvulling 3 kg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/liza-800g-eend</t>
+          <t>https://doglife.be/product/yoggies-ecologisch-kattenbakvulling-3-kg</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3,60</t>
+          <t>9,10</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.622</v>
+        <v>0.615</v>
       </c>
       <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>400g-yoggies-kachni-konzerva-s-hruskou-a-jahlami</t>
+          <t>10kg-yoggies-minigranule-iberico-veprove-maso-s-jablky-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>400 g Yoggies kachní konzerva s hruškou a jáhlami</t>
+          <t>10 kg Yoggies Ibérico varkensvlees met appel, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LIZA 400g Eend</t>
+          <t>Yoggies Ibérico varkensvlees met appels, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/liza-400g-eend</t>
+          <t>https://doglife.be/product/iberico-met-appels-hypoallergeen</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2,00</t>
+          <t>37,10</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.622</v>
+        <v>0.614</v>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yoggies-ekologicke-stelivo-pro-kocky-3kg</t>
+          <t>20kg-yoggies-minigranule-iberico-veprove-maso-s-jablky-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yoggies Ekologické stelivo pro kočky 3 kg</t>
+          <t>20 kg Yoggies Ibérico varkensvlees met appel, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yoggies – Ecologisch kattenbakvulling 3 kg</t>
+          <t>Yoggies Ibérico varkensvlees met appels, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-ecologisch-kattenbakvulling-3-kg</t>
+          <t>https://doglife.be/product/iberico-met-appels-hypoallergeen</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9,10</t>
+          <t>37,10</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.615</v>
+        <v>0.614</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20kg-yoggies-iberico-veprove-maso-s-jablky-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>5kg-yoggies-minigranule-iberico-veprove-maso-s-jablky-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20 kg Yoggies Ibérico vepřové maso s jablky, granule lisované za studena s probiotiky</t>
+          <t>5 kg Yoggies Ibérico varkensvlees met appel, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1410,19 +1410,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.611</v>
+        <v>0.614</v>
       </c>
       <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10kg-yoggies-iberico-veprove-maso-s-jablky-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>2kg-yoggies-minigranule-iberico-veprove-maso-s-jablky-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10 kg Yoggies Ibérico vepřové maso s jablky, granule lisované za studena s probiotiky</t>
+          <t>2 kg Yoggies Ibérico varkensvlees met appel, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1441,34 +1441,34 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.611</v>
+        <v>0.614</v>
       </c>
       <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>650g-yoggies-varena-potrava-pro-psy-kruti-a-kralici-maso-s-dynovymi-seminky-a-kloubni-vyzivou</t>
+          <t>2kg-jehneci-a-bila-ryba-granule-lisovane-za-studena-s-probiotiky-yoggies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>650 g Yoggies Vařená potrava pro psy – krůtí a králičí maso s dýňovými semínky</t>
+          <t>2 kg Yoggies lamsvlees &amp; witvis, koudgeperste brokken met probiotica</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>650g Yoggies Gekookt Hondenvoer – Kalkoen met Boekweit</t>
+          <t>2 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste  MINI korrels met probiotica</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-650g-gekookt-hondenvoer-kalkoen-met-boekweit</t>
+          <t>https://doglife.be/product/2-kg-yoggies-vet-gastro-sensitive-met-kalkoenvlees-koudgeperste-mini-korrels-met-probiotica</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6,90</t>
+          <t>19,70</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1479,27 +1479,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5kg-yoggies-iberico-veprove-maso-s-jablky-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>5-kg-jehneci-a-bila-ryba-granule-lisovane-za-studena-s-probiotiky-yoggies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5 kg Yoggies Ibérico vepřové maso s jablky, granule lisované za studena s probiotiky</t>
+          <t>5 kg Yoggies lamsvlees &amp; witvis, koudgeperste brokken met probiotica</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yoggies Ibérico varkensvlees met appels, koudgeperste korrels met probiotica</t>
+          <t>5 kg Yoggies VET Gastro Sensitive met kalkoen, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/iberico-met-appels-hypoallergeen</t>
+          <t>https://doglife.be/product/vet-gastro-sensitive-met-kalkoen-en-probiotica-5-kg</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37,10</t>
+          <t>49,40</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1510,372 +1510,372 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2kg-yoggies-iberico-veprove-maso-s-jablky-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>lupo-gelenkol-olej-gelenk-akut-500-ml-doplnek-potravy-pro-psy-pro-vyzivu-kosti-a-kloubu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2 kg Yoggies Ibérico vepřové maso s jablky, granule lisované za studena s probiotiky</t>
+          <t>LUPO GelenkÖl olie - Gelenk Akut 500 ml</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yoggies Ibérico varkensvlees met appels, koudgeperste korrels met probiotica</t>
+          <t>LUPO GelenkÖl (gewrichten)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/iberico-met-appels-hypoallergeen</t>
+          <t>https://doglife.be/product/lupo-gelenkol</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>37,10</t>
+          <t>30,00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.611</v>
+        <v>0.608</v>
       </c>
       <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>650g-yoggies-varena-potrava-pro-psy-kruti-maso-s-pohankou-a-kloubni-vyzivou</t>
+          <t>sodapup-mandala-nylonova-senzoricka-miska-ruzova</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>650 g Yoggies Vařená potrava pro psy – krůtí maso s pohankou</t>
+          <t>SodaPup Mandala, sensorische kom van nylon - roze</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>650g Yoggies Gekookt Hondenvoer – Kalkoen met Boekweit</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-650g-gekookt-hondenvoer-kalkoen-met-boekweit</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6,90</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.611</v>
+        <v>0.604</v>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>650g-yoggies-varena-potrava-pro-psy-kureci-maso-s-ryzi</t>
+          <t>sodapup-mandala-nylonova-senzoricka-miska-fialova</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>650 g Yoggies Vařená potrava pro psy – kuřecí maso s rýží</t>
+          <t>SodaPup Mandala, sensorische kom van nylon - paars</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>650g Yoggies Gekookt Hondenvoer – Kip met Rijst</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-650g-gekookt-hondenvoer-kip-met-rijst</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6,40</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.61</v>
+        <v>0.597</v>
       </c>
       <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>200g-yoggies-jehneci-konzerva-s-bramborem-a-karotkou</t>
+          <t>12x85g-yoggies-misticka-pro-kocky-s-lososem-a-tunakem-v-lahodne-zele-omacce</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>200 g Yoggies jehněčí konzerva s bramborem a karotkou</t>
+          <t>11+1 85 g Yoggies kuipje voor katten met zalm en tonijn in heerlijke geleisaus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>200g Yoggies blik lam met aardappelen en wortelen</t>
+          <t>Yoggies Gevriesdroogd ZALM 85 g</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-blik-lam-met-aarappelen-en-wortelen-200-g</t>
+          <t>https://doglife.be/product/yoggies-gevriesdroogd-zalm-85-g</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1,50</t>
+          <t>10,30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.609</v>
+        <v>0.596</v>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5-1-yoggies-jehneci-konzerva-s-bramborem-a-karotkou-400g</t>
+          <t>yoggies-misticky-pro-kocky-s-tunakem-a-lososem-v-zele-omacce-85g</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5+1 Yoggies jehněčí konzerva s bramborem a karotkou 400 g</t>
+          <t>85 g Yoggies kuipje voor katten met zalm, tonijn en geleisaus</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>400g Yoggies blik lam met aardappelen en wortelen</t>
+          <t>Yoggies Gevriesdroogd ZALM 85 g</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-lamsvlees-in-blik-met-aardappelen-en-wortelen-400-g</t>
+          <t>https://doglife.be/product/yoggies-gevriesdroogd-zalm-85-g</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>10,30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.609</v>
+        <v>0.596</v>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5-1-yoggies-jehneci-konzerva-s-bramborem-a-karotkou-800g</t>
+          <t>700g-b-a-r-f-losos-kun-kruta-s-probiotiky</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5+1 Yoggies jehněčí konzerva s bramborem a karotkou 800 g</t>
+          <t>700 g Yoggies B.A.R.F. Zalm, paard, kalkoen met probiotica</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>800g Yoggies blik lam met aardappelen en wortelen</t>
+          <t>700 g Yoggies BARF 100% kalkoen met probiotica Rauw vlees voor honden</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/800g-yoggies-blik-lam-met-aardappelen-en-wortelen-copy</t>
+          <t>https://doglife.be/product/700-g-yoggies-barf-100-kalkoen-met-probiotica-rauw-vlees-voor-honden</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5,50</t>
+          <t>4,30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.609</v>
+        <v>0.585</v>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5-1-yoggies-jehneci-konzerva-s-bramborem-a-karotkou-200g</t>
+          <t>10kg-yoggies-jehneci-maso-bila-ryba-granule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5+1 Yoggies jehněčí konzerva s bramborem a karotkou 200 g</t>
+          <t>10 kg Yoggies lamsvlees &amp; witvis, koudgeperste brokken met probiotica</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>200g Yoggies blik lam met aardappelen en wortelen</t>
+          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-blik-lam-met-aarappelen-en-wortelen-200-g</t>
+          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1,50</t>
+          <t>33,20</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.609</v>
+        <v>0.583</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>800g-yoggies-jehneci-konzerva-s-bramborem-a-karotkou</t>
+          <t>10kg-yoggies-vet-insect-derma-s-hmyzim-proteinem-granule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>800 g Yoggies jehněčí konzerva s bramborem a karotkou</t>
+          <t>10 kg Yoggies VET Insect Derma met insectenproteïne, koudgeperste brokken met probiotica</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>800g Yoggies blik lam met aardappelen en wortelen</t>
+          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/800g-yoggies-blik-lam-met-aardappelen-en-wortelen-copy</t>
+          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5,50</t>
+          <t>33,20</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.609</v>
+        <v>0.583</v>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>400g-yoggies-jehneci-konzerva-s-bramborem-a-karotkou</t>
+          <t>10kg-yoggies-vet-gastro-sensitive-s-krutim-masem-granule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>400 g Yoggies jehněčí konzerva s bramborem a karotkou</t>
+          <t>10 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste brokken met probiotica</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>400g Yoggies blik lam met aardappelen en wortelen</t>
+          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-lamsvlees-in-blik-met-aardappelen-en-wortelen-400-g</t>
+          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>33,20</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.609</v>
+        <v>0.583</v>
       </c>
       <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>lupo-gelenkol-olej-gelenk-akut-500-ml-doplnek-potravy-pro-psy-pro-vyzivu-kosti-a-kloubu</t>
+          <t>20kg-jehneci-a-bila-ryba-granule-lisovane-za-studena-yoggies</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LUPO GelenkÖl olej - Gelenk Akut 500 ml</t>
+          <t>20 kg Yoggies lamsvlees &amp; witvis, koudgeperste brokken met probiotica</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LUPO GelenkÖl (gewrichten)</t>
+          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/lupo-gelenkol</t>
+          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>30,00</t>
+          <t>33,20</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.608</v>
+        <v>0.583</v>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>650g-yoggies-varena-potrava-pro-psy-hovezi-maso-s-quinoou-a-kloubni-vyzivou</t>
+          <t>10kg-yoggies-vet-veggie-bez-masa-granule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>650 g Yoggies Vařená potrava pro psy – hovězí maso s quinoou</t>
+          <t>10 kg Yoggies VET Veggie vleesvrij, koudgeperste brokken met probiotica</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>650g Yoggies Gekookt Hondenvoer – Rundvlees met Quinoa</t>
+          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-650g-gekookt-hondenvoer-rundvlees-met-quinoa</t>
+          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>7,40</t>
+          <t>33,20</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.602</v>
+        <v>0.583</v>
       </c>
       <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1-5kg-yoggies-b-a-r-f-pro-kocky-kureci-komplet-s-lososem-a-brusinkami</t>
+          <t>15kg-jehneci-a-bila-ryba-granule-lisovane-za-studena-yoggies</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6x250 g Yoggies BARF pro kočky Kuřecí komplet s lososem a brusinkami</t>
+          <t>15 kg Yoggies lamsvlees &amp; witvis, koudgeperste brokken met probiotica</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1,5 kg (6x250gr)Yoggies BARF Kip en Zalm Compleet met Veenbessen met Probiotica Rauw Voedsel voor Katten</t>
+          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/6x250-gr-b-a-r-f-kip-met-zalm</t>
+          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15,20</t>
+          <t>33,20</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.598</v>
+        <v>0.583</v>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5+1 Yoggies hovězí konzerva s ostropestřcem mariánským 800 g</t>
+          <t>5+1 Yoggies rund blikvoer met mariadistel 800 g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>800 g Yoggies hovězí konzerva s ostropestřcem mariánským</t>
+          <t>800 g Yoggies rund blikvoer met mariadistel</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Yoggies DogProBio, probiotická směs pro psy 130 g</t>
+          <t>Yoggies DogProBio, probiotische mix voor honden 130 g</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1975,2544 +1975,1924 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>700g-b-a-r-f-losos-kun-kruta-s-probiotiky</t>
+          <t>yoggies-jogurt-pro-psy-a-kocky-150g</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>700 g Yoggies B.A.R.F. Losos, kůň, krůta s probiotiky</t>
+          <t>Yoggies yoghurt voor honden en katten 150 g - voordeelverpakking 6 of 12 stuks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>700 g Yoggies BARF 100% kalkoen met probiotica Rauw vlees voor honden</t>
+          <t>Freedog Parfums voor honden en katten 150 ml</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/700-g-yoggies-barf-100-kalkoen-met-probiotica-rauw-vlees-voor-honden</t>
+          <t>https://doglife.be/product/freedog-parfums-voor-honden-en-katten-150-ml</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4,30</t>
+          <t>16,20</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.57</v>
+        <v>0.569</v>
       </c>
       <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10kg-yoggies-kruti-maso-jahly-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>2kg-yoggies-vet-veggie-bez-masa-minigranule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10 kg Yoggies Krůtí maso &amp; jáhly, granule lisované za studena s probiotiky</t>
+          <t>2 kg Yoggies VET Veggie vleesvrij, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Yoggies korrels voor katten met kalkoenvlees, koudgeperst met probiotica</t>
+          <t>2 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste  MINI korrels met probiotica</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-cat-kalkoen-korrels-proteine</t>
+          <t>https://doglife.be/product/2-kg-yoggies-vet-gastro-sensitive-met-kalkoenvlees-koudgeperste-mini-korrels-met-probiotica</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6,20</t>
+          <t>19,70</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20-kg-monoproteinove-granule-yoggies-s-krutim-masem-a-jahly-lisovane-za-studena-s-probiotiky</t>
+          <t>500g-luposan-moorliquid-susena-raselina-pro-podporu-zdraveho-zazivani</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20 kg Yoggies Krůtí maso &amp; jáhly, granule lisované za studena s probiotiky</t>
+          <t>500 g, Luposan MoorLiquid. Vloeibaar veen ter ondersteuning van een gezonde spijsvertering</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yoggies korrels voor katten met kalkoenvlees, koudgeperst met probiotica</t>
+          <t>Yoggies voor gezonde gewrichten 500g (korrels)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-cat-kalkoen-korrels-proteine</t>
+          <t>https://doglife.be/product/gezonde-gewrichten-600-g</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>6,20</t>
+          <t>38,00</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.553</v>
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>15-kg-monoproteinove-granule-yoggies-s-krutim-masem-a-jahly-lisovane-za-studena-s-probiotiky</t>
+          <t>500ml-lupoderm-olej-a-doplnek-potravy-pro-zdravou-kuzi-a-srst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15 kg Yoggies Krůtí maso &amp; jáhly, granule lisované za studena s probiotiky</t>
+          <t>500 ml, LupoDerm - olie en voedingssupplement voor een gezonde huid en vacht</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yoggies korrels voor katten met kalkoenvlees, koudgeperst met probiotica</t>
+          <t>Yoggies voor gezonde gewrichten 500g (korrels)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-cat-kalkoen-korrels-proteine</t>
+          <t>https://doglife.be/product/gezonde-gewrichten-600-g</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6,20</t>
+          <t>38,00</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.553</v>
       </c>
       <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2kg-yoggies-kruti-masojahly-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>soda-pup-kulata-lizaci-podlozka-rajska-zahrada-zelena</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2 kg Yoggies Krůtí maso &amp; jáhly, granule lisované za studena s probiotiky</t>
+          <t>SodaPup ronde likmat Paradijstuin - groen</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Yoggies korrels voor katten met kalkoenvlees, koudgeperst met probiotica</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-cat-kalkoen-korrels-proteine</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6,20</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.542</v>
       </c>
       <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5-kg-monoproteinove-granule-yoggies-s-krutim-masem-a-jahly-lisovane-za-studena-s-probiotiky</t>
+          <t>sodapup-lizaci-podlozka-flower-power-ruzova-20x20cm</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5 kg Yoggies Krůtí maso &amp; jáhly, granule lisované za studena s probiotiky</t>
+          <t>SodaPup likmat flower power, roze</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yoggies korrels voor katten met kalkoenvlees, koudgeperst met probiotica</t>
+          <t>Flower´s Bone</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-cat-kalkoen-korrels-proteine</t>
+          <t>https://doglife.be/product/flowers-bone</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6,20</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.531</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6-1-zdarma-7x-650g-yoggies-varena-potrava-pro-psy-losos-a-bila-ryba-s-chia-seminky</t>
+          <t>sodapup-lizaci-podlozka-flower-power-mala-18-x-13cm-ruzova</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6+1 zdarma (7x650 g) Yoggies Vařená potrava pro psy – losos a bílá ryba s chia semínky</t>
+          <t>SodaPup likmat flower power klein, roze</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FARMKA DOG met zalm</t>
+          <t>Flower´s Bone</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/farmka-dog-met-zalm</t>
+          <t>https://doglife.be/product/flowers-bone</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2,50</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.556</v>
+        <v>0.531</v>
       </c>
       <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6-1-zdarma-7x-150g-yoggies-varena-potrava-pro-psy-losos-a-bila-ryba-s-chia-seminky</t>
+          <t>12x85g-yoggies-misticka-pro-kocky-s-kurecim-masem-a-zele-omackou</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6+1 zdarma (7x150 g) Yoggies Vařená potrava pro psy – losos a bílá ryba s chia semínky</t>
+          <t>11+1 85 g Yoggies kuipje voor katten met kip in geleisaus</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FARMKA DOG met zalm</t>
+          <t>Fitmin For Life – cat Chicken zakje 85 g</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/farmka-dog-met-zalm</t>
+          <t>https://doglife.be/product/fitmin-for-life-chicken-zakje-85-g</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2,50</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.556</v>
+        <v>0.521</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>150g-yoggies-varena-potrava-pro-psy-losos-a-bila-ryba-s-chia-seminky-a-kloubni-vyzivou</t>
+          <t>lickimat-playdate-lizaci-podlozka-20-x-20-cm</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>150 g Yoggies Vařená potrava pro psy – losos a bílá ryba s chia semínky</t>
+          <t>LickiMat Playdate likmat 20x20cm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FARMKA DOG met zalm</t>
+          <t>LIKMAT – voor snoepjes 20x20cm, TRIXIE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/farmka-dog-met-zalm</t>
+          <t>https://doglife.be/product/likmat-voor-snoepjes-20x20cm-trixie</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2,50</t>
+          <t>12,30</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.556</v>
+        <v>0.521</v>
       </c>
       <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>650g-yoggies-varena-potrava-pro-psy-losos-a-bila-ryba-s-chia-seminky-a-kloubni-vyzivou</t>
+          <t>85g-yoggies-misticky-s-kurecim-masem-a-zele-omackou-pro-kocky</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>650 g Yoggies Vařená potrava pro psy – losos a bílá ryba s chia semínky</t>
+          <t>85 g Yoggies kuipje voor katten met kip in geleisaus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FARMKA DOG met zalm</t>
+          <t>Fitmin For Life – cat Chicken zakje 85 g</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/farmka-dog-met-zalm</t>
+          <t>https://doglife.be/product/fitmin-for-life-chicken-zakje-85-g</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2,50</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.556</v>
+        <v>0.521</v>
       </c>
       <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1-5kg-yoggies-b-a-r-f-hovezi-a-kruti-komplet-s-brusinkami-a-konopnym-olejem-s-probiotiky</t>
+          <t>yoggies-latkova-cestovni-miska</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6x250 g Yoggies B.A.R.F. Hovězí a krůtí komplet s brusinkami a konopným olejem s probiotiky</t>
+          <t>Yoggies stoffen reiskom</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1,5 kg (6x250gr) Yoggies BARF Rund en Kalkoen Compleet met Veenbessen en Hennepolie met Probiotica Rauw Voedsel voor Katten</t>
+          <t>LUPO NATURAL – ALGEN – vitale stoffen uit rode, groene en bruine algen</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/6x250-g-b-a-r-f-rundvlees-en-kalkoen-compleet</t>
+          <t>https://doglife.be/product/lupo-natural-algen-vitale-stoffen-uit-rode-groene-en-bruine-algen</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18,40</t>
+          <t>16,90</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.555</v>
+        <v>0.519</v>
       </c>
       <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10kg-yoggies-kureci-hovezi-maso-minigranule-lisovane-za-studena-s-probiotiky</t>
+          <t>degustacni-menu-5-1-zdarma-6x-150g-yoggies-varena-potrava-pro-psy</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10 kg Yoggies Kuřecí &amp; hovězí maso, MINIgranule lisované za studena s probiotiky</t>
+          <t>Proefmenu 5+1 gratis (6x150 g) Yoggies gekookt hondenvoer</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
+          <t>6x150g Yoggies yoghurt voor honden en katten</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
+          <t>https://doglife.be/product/yoghurt-yoggies-6-x-150-g</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>33,20</t>
+          <t>12,60</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.551</v>
+        <v>0.516</v>
       </c>
       <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2-kg-minigranule-kureci-a-hovezi-maso-minigranule-lisovane-za-studena-s-probiotiky-yoggies</t>
+          <t>roztok-na-cisteni-usi-senzi-auris-pro-psy-a-kocky-100-ml</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2 kg Yoggies Kuřecí &amp; hovězí maso, MINIgranule lisované za studena s probiotiky</t>
+          <t>SENZI-AURIS oorreinigingsoplossing voor honden en katten 100 ml</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
+          <t>Yoggies Chlorella voor honden 100g</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
+          <t>https://doglife.be/product/chlorella</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>33,20</t>
+          <t>8,70</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.551</v>
+        <v>0.515</v>
       </c>
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5-kg-minigranule-kureci-a-hovezi-maso-minigranule-lisovane-za-studena-s-probiotiky-yoggies</t>
+          <t>tekuty-vosk-felleol-pro-upravu-srsti-psu-kocek-koni-100-ml</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5 kg Yoggies Kuřecí &amp; hovězí maso, MINIgranule lisované za studena s probiotiky</t>
+          <t>FELLEOL vloeibare was voor de vachtverzorging van honden en katten 100 ml</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
+          <t>Yoggies Chlorella voor honden 100g</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
+          <t>https://doglife.be/product/chlorella</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>33,20</t>
+          <t>8,70</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.551</v>
+        <v>0.515</v>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>15-kg-minigranule-kureci-a-hovezi-maso-minigranule-lisovane-za-studena-yoggies</t>
+          <t>100g-verm-x-pamlsek-a-prirodni-prostredek-na-pravidelne-bezchemicke-odcerveni-psa</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15 kg Yoggies Kuřecí &amp; hovězí maso, MINIgranule lisované za studena s probiotiky</t>
+          <t>100 g, Verm-X, snack en natuurlijk middel ter ondersteuning van een "chemievrije" ontworming bij de hond</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
+          <t>Yoggies Chlorella voor honden 100g</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
+          <t>https://doglife.be/product/chlorella</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>33,20</t>
+          <t>8,70</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.551</v>
+        <v>0.515</v>
       </c>
       <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>500ml-lupoderm-olej-a-doplnek-potravy-pro-zdravou-kuzi-a-srst</t>
+          <t>zeleny-psi-motylek-velikost-m-9-cm</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>500 ml, LupoDerm - olej a doplněk potravy pro zdravou kůži a srst</t>
+          <t>Groen strikje voor de hond</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Yoggies Zalm Olie voor Honden en Katten 500 ml</t>
+          <t>Happy Dog knuffel groen 28 cm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/zalmolie-500-ml</t>
+          <t>https://doglife.be/product/happy-dog-knuffel-groen-28-cm</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10,00</t>
+          <t>12,95</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.547</v>
+        <v>0.509</v>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2kg-yoggies-vet-veggie-bez-masa-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>sodapup-lizaci-podlozka-puzzle-20-x-20cm-modra</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2 kg Yoggies VET Veggie bez masa, granule lisované za studena s probiotiky</t>
+          <t>SodaPup likmat puzzel, blauw</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste  MINI korrels met probiotica</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/2-kg-yoggies-vet-gastro-sensitive-met-kalkoenvlees-koudgeperste-mini-korrels-met-probiotica</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19,70</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.545</v>
+        <v>0.507</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4-8-kg-yoggies-granule-pro-kocky-s-kurecim-masem-lisovane-za-studena-s-probiotiky-darek-zdarma</t>
+          <t>sodapup-love-lizaci-podlozka-cervena-20-x-20cm</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4,8 kg Yoggies Granule pro kočky s kuřecím masem lisované za studena s probiotiky + DÁREK ZDARMA</t>
+          <t>SodaPup Love likmat, rood</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yoggies korrels voor katten met kip, koudgeperst met probiotica</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-cat-kip-korrels-proteine</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.538</v>
+        <v>0.506</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4-8-yoggies-granule-pro-kocky-s-krocanim-masem-lisovane-za-studena-darek</t>
+          <t>yoggies-multifunkcni-nakrcnik</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4,8 kg Yoggies  Granule pro kočky s krocaním masem, lisované za studena s probiotiky + DÁREK</t>
+          <t>Yoggies multifunctionele nekwarmer</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Yoggies korrels voor katten met kip, koudgeperst met probiotica</t>
+          <t>Multifunctionele deken 100×70</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-cat-kip-korrels-proteine</t>
+          <t>https://doglife.be/product/multifunctionele-deken-100x70</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>7,40</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>yoggies-granule-s-krocanim-masem-pro-kocky-lisovane-za-studena-s-probiotiky-1200g</t>
+          <t>sodapup-lizaci-podlozka-zombie-20x20cm-cerna</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1,2 kg Yoggies Granule pro kočky s krocaním masem, lisované za studena s probiotiky</t>
+          <t>SodaPup likmat zombie, zwart</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yoggies korrels voor katten met kip, koudgeperst met probiotica</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-cat-kip-korrels-proteine</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.538</v>
+        <v>0.497</v>
       </c>
       <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>yoggies-granule-s-krocanim-masem-pro-kocky-lisovane-za-studena-s-probiotiky-400g</t>
+          <t>700g-b-a-r-f-losos-a-kralik-s-probiotiky</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>400 g Yoggies Granule pro kočky s krocaním masem, lisované za studena s probiotiky</t>
+          <t>700 g B.A.R.F. Zalm en konijn met probiotica</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Yoggies Maag en darmen met probiotica voor honden (korrels) 400g</t>
+          <t>700 g Yoggies BARF 100% kalkoen met probiotica Rauw vlees voor honden</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/maag-en-darmen-met-probiotica-voor-honden-400g</t>
+          <t>https://doglife.be/product/700-g-yoggies-barf-100-kalkoen-met-probiotica-rauw-vlees-voor-honden</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>34,20</t>
+          <t>4,30</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.538</v>
+        <v>0.496</v>
       </c>
       <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>yoggies-granule-s-kurecim-masem-pro-kocky-lisovane-za-studena-s-probiotiky-1200g</t>
+          <t>5-1-yoggies-kozi-konzerva-s-bramborem-a-mrkvi-800g</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1,2 kg Yoggies Granule pro kočky s kuřecím masem, lisované za studena s probiotiky</t>
+          <t>5+1 Yoggies geit blikvoer met aardappel en wortel 800 g</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yoggies korrels voor katten met kip, koudgeperst met probiotica</t>
+          <t>800g Yoggies blik geit met aardappelen en wortelen</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-cat-kip-korrels-proteine</t>
+          <t>https://doglife.be/product/yoggies-geit-met-aardappelen-en-wortelen-800-g</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>5,30</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.538</v>
+        <v>0.496</v>
       </c>
       <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>yoggies-granule-s-kurecim-masem-pro-kocky-lisovane-za-studena-s-probiotiky-400g</t>
+          <t>800g-yoggies-kozi-konzerva-s-bramborem-a-mrkvi</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>400 g Yoggies Granule pro kočky s kuřecím masem, lisované za studena s probiotiky</t>
+          <t>800 g Yoggies geit blikvoer met aardappel en wortel</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yoggies Maag en darmen met probiotica voor honden (korrels) 400g</t>
+          <t>800g Yoggies blik geit met aardappelen en wortelen</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/maag-en-darmen-met-probiotica-voor-honden-400g</t>
+          <t>https://doglife.be/product/yoggies-geit-met-aardappelen-en-wortelen-800-g</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>34,20</t>
+          <t>5,30</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.538</v>
+        <v>0.496</v>
       </c>
       <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>yoggies-konzerva-hovezi-s-ostropestrcem-marianskym</t>
+          <t>soda-pup-lizaci-podlozka-podzim</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Yoggies konzerva Hovězí s ostropestřcem mariánským</t>
+          <t>SodaPup likmat herfst, geel</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>400g Yoggies blik rundvlees met mariadistel</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-monoproteine-rund-met-mariadistel-400g</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>3,30</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.537</v>
+        <v>0.493</v>
       </c>
       <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5-1-yoggies-jeleni-konzerva-s-pohankou-a-brusinkami-400g</t>
+          <t>sodapup-lizaci-podlozka-honey-zluta-20x20cm</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5+1 Yoggies jelení konzerva s pohankou a brusinkami 400 g</t>
+          <t>SodaPup likmat honey, geel</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Falco TIM 400g wild</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/falco-tim-400g-wild</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2,00</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.537</v>
+        <v>0.493</v>
       </c>
       <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>400g-yoggies-jeleni-konzerva-s-pohankou-a-brusinkami</t>
+          <t>sodapup-lizaci-podlozka-zombie-20x20cm-oranzova</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>400 g Yoggies Jelení konzerva s pohankou a brusinkami</t>
+          <t>SodaPup likmat zombie, oranje</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Falco TIM 400g wild</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/falco-tim-400g-wild</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2,00</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.537</v>
+        <v>0.491</v>
       </c>
       <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1000g-syrove-maso-kruti-stehna</t>
+          <t>sodapup-vceli-plastev-nylonova-senzoricka-miska-zluta</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1 kg Yoggies B.A.R.F. Krůtí stehna</t>
+          <t>SodaPup Honingraat, sensorische kom van nylon - geel</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Vlees voor B.A.R.F. – Kalkoen billen 1 kg (diepgevroren)</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/vlees-voor-b-a-r-f-kalkoen-billen-1-kg-diepgevroren</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>4,70</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.535</v>
+        <v>0.491</v>
       </c>
       <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1000g-syrove-maso-kruti-kridla</t>
+          <t>yoggies-balicek-na-cestu-pro-kote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1 kg Yoggies B.A.R.F. Krůtí křídla</t>
+          <t>Yoggies reispakket voor het kitten</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vlees voor B.A.R.F. – Kalkoen billen 1 kg (diepgevroren)</t>
+          <t>FITMIN For Life Kitten 1,8 kg</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/vlees-voor-b-a-r-f-kalkoen-billen-1-kg-diepgevroren</t>
+          <t>https://doglife.be/product/fitmin-for-life-kitten-18-kg</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>4,70</t>
+          <t>11,90</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.535</v>
+        <v>0.483</v>
       </c>
       <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1000g-syrove-maso-kruti-zaludky</t>
+          <t>1-kg-b-a-r-f-kureci-stehna-a-orezy-syrove-maso-pro-psy-a-kocky</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1 kg Yoggies B.A.R.F. Krůtí žaludky</t>
+          <t>1 kg Yoggies B.A.R.F. Kippenpoten en snippers</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Vlees voor B.A.R.F. – Kalkoen billen 1 kg (diepgevroren)</t>
+          <t>Gedroogde Kippenpoten 5 stuks</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/vlees-voor-b-a-r-f-kalkoen-billen-1-kg-diepgevroren</t>
+          <t>https://doglife.be/product/gedroogde-kippenklauwen-5-stuks</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>4,70</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0.535</v>
+        <v>0.483</v>
       </c>
       <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>sodapup-lizaci-podlozka-flower-power-ruzova-20x20cm</t>
+          <t>2-kg-minigranule-yoggies-jehneci-a-bila-ryba-granule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SodaPup Lízací podložka flower power, růžová</t>
+          <t>2 kg Yoggies lamsvlees &amp; witvis, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Flower´s Bone</t>
+          <t>2 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste  MINI korrels met probiotica</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/flowers-bone</t>
+          <t>https://doglife.be/product/2-kg-yoggies-vet-gastro-sensitive-met-kalkoenvlees-koudgeperste-mini-korrels-met-probiotica</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>19,70</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0.531</v>
+        <v>0.482</v>
       </c>
       <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sodapup-lizaci-podlozka-flower-power-mala-18-x-13cm-ruzova</t>
+          <t>5kg-minigranule-yoggies-jehneci-a-bila-ryba-granule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SodaPup lízací podložka flower power malá, růžová</t>
+          <t>5 kg Yoggies lamsvlees &amp; witvis, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Flower´s Bone</t>
+          <t>5 kg Yoggies VET Gastro Sensitive met kalkoen, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/flowers-bone</t>
+          <t>https://doglife.be/product/vet-gastro-sensitive-met-kalkoen-en-probiotica-5-kg</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>49,40</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0.531</v>
+        <v>0.482</v>
       </c>
       <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5-1-yoggies-klokani-konzerva-s-dyni-a-topinamburem-400-g</t>
+          <t>plysova-hracka-pro-psy-mys-zelena</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5+1 Yoggies Klokaní konzerva s dýní a topinamburem 400 g</t>
+          <t>Pluche hondenspeeltje – muis, groen</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>400g Yoggies blik kalkoen met bataten</t>
+          <t>Ballenkooi met muis</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/400g-yoggies-blik-kalkoen-met-bataten</t>
+          <t>https://doglife.be/product/ballenkooi-met-muis</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>1,90</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.524</v>
+        <v>0.481</v>
       </c>
       <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>400g-yoggies-klokani-konzerva-pro-psy-s-dyni</t>
+          <t>yoggies-balicek-na-cestu-pro-stene-kureci</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>400 g Yoggies Klokaní konzerva s dýní a topinamburem</t>
+          <t>Yoggies reispakket voor de puppy - Kip &amp; rund</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>400g Yoggies blik kalkoen met bataten</t>
+          <t>Fitmin Dog Medium Maxi Puppy Lamb Beef 12 kg</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/400g-yoggies-blik-kalkoen-met-bataten</t>
+          <t>https://doglife.be/product/fitmin-dog-medium-maxi-puppy-lamb-beef-12-kg</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>70,20</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.524</v>
+        <v>0.48</v>
       </c>
       <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5-1-yoggies-drubezi-konzerva-se-zeleninou-a-ovesnymi-vlockami-400g</t>
+          <t>250ml-lupoderm-olej-a-doplnek-potravy-pro-zdravou-kuzi-a-srst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5+1 Yoggies drůbeží konzerva se zeleninou a ovesnými vločkami 400 g</t>
+          <t>250 ml, LupoDerm - olie en voedingssupplement voor een gezonde huid en vacht</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>400g Yoggies blik kalkoen met bataten</t>
+          <t>LUPO Premium Wildfish Oil 250 ml</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/400g-yoggies-blik-kalkoen-met-bataten</t>
+          <t>https://doglife.be/product/lupo-premium-wildfish-oil-250-ml</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>20,90</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.524</v>
+        <v>0.48</v>
       </c>
       <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5-1-yoggies-kozi-konzerva-s-bramborem-a-mrkvi-400g</t>
+          <t>sodapup-lizaci-podlozka-puzzle-20-x-20cm-ruzova</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5+1 Yoggies kozí konzerva s bramborem a mrkví 400 g</t>
+          <t>SodaPup likmat puzzel, roze</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>400g Yoggies blik kalkoen met bataten</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/400g-yoggies-blik-kalkoen-met-bataten</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0.524</v>
+        <v>0.479</v>
       </c>
       <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5-1-yoggies-jeleni-konzerva-s-pohankou-a-brusinkami-800g</t>
+          <t>sodapup-senzoricka-miska-psi-na-baru-modra</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5+1 Yoggies jelení konzerva s pohankou a brusinkami 800 g</t>
+          <t>SodaPup sensorische kom Honden aan de bar – blauw</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>800g Yoggies blik kalkoen met bataten</t>
+          <t>Roestvrijstalen siliconen kom Blauw 600ml</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/800g-yoggies-blik-kalkoen-met-bataten</t>
+          <t>https://doglife.be/product/roestvrijstalen-siliconen-kom-blauw-600ml</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>6,20</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.524</v>
+        <v>0.477</v>
       </c>
       <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>800g-yoggies-jeleni-konzerva-s-pohankou-a-brusinkami</t>
+          <t>5-1-yoggies-jehneci-konzerva-s-bramborem-a-karotkou-800g</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>800 g Yoggies jelení konzerva s pohankou a brusinkami</t>
+          <t>5+1 Yoggies lam blikvoer met aardappel en wortel 800 g</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>800g Yoggies blik kalkoen met bataten</t>
+          <t>Fitmin For Life – LAM voor Honden 800 g</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/800g-yoggies-blik-kalkoen-met-bataten</t>
+          <t>https://doglife.be/product/fitmin-for-life-lam-voor-honden-800-g</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>6,20</t>
+          <t>4,50</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0.524</v>
+        <v>0.476</v>
       </c>
       <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>400g-yoggies-kozi-konzerva-s-bramborem-a-mrkvi</t>
+          <t>800g-yoggies-jehneci-konzerva-s-bramborem-a-karotkou</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>400 g Yoggies kozí konzerva s bramborem a mrkví</t>
+          <t>800 g Yoggies lam blikvoer met aardappel en wortel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>400g Yoggies blik kalkoen met bataten</t>
+          <t>Fitmin For Life – LAM voor Honden 800 g</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/400g-yoggies-blik-kalkoen-met-bataten</t>
+          <t>https://doglife.be/product/fitmin-for-life-lam-voor-honden-800-g</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>4,50</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0.524</v>
+        <v>0.476</v>
       </c>
       <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>400g-yoggies-drubezi-konzerva-se-zeleninou-a-ovesnymi-vlockami</t>
+          <t>yoggies-balicek-na-cestu-active-kachni</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>400 g Yoggies drůbeží konzerva se zeleninou a ovesnými vločkami</t>
+          <t>Yoggies reispakket voor de puppy - Active eend</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>400g Yoggies blik kalkoen met bataten</t>
+          <t>LIZA 400g Eend</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/400g-yoggies-blik-kalkoen-met-bataten</t>
+          <t>https://doglife.be/product/liza-400g-eend</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>2,00</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.524</v>
+        <v>0.472</v>
       </c>
       <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10kg-yoggies-minigranule-iberico-veprove-maso-s-jablky-lisovane-za-studena-s-probiotiky</t>
+          <t>sodapup-lizaci-podlozka-lotus-svetle-ruzova</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>10 kg Yoggies Ibérico vepřové maso s jablky, MINIgranule lisované za studena s probiotiky</t>
+          <t>SodaPup likmat Lotus - lichtroze</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Yoggies Ibérico varkensvlees met appels, koudgeperste korrels met probiotica</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/iberico-met-appels-hypoallergeen</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>37,10</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0.516</v>
+        <v>0.471</v>
       </c>
       <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20kg-yoggies-minigranule-iberico-veprove-maso-s-jablky-lisovane-za-studena-s-probiotiky</t>
+          <t>sodapup-lizaci-podlozka-kosticky-20x20cm-fialova</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>20 kg Yoggies Ibérico vepřové maso s jablky, MINIgranule lisované za studena s probiotiky</t>
+          <t>SodaPup likmat blokjes, paars</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Yoggies Ibérico varkensvlees met appels, koudgeperste korrels met probiotica</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/iberico-met-appels-hypoallergeen</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>37,10</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0.516</v>
+        <v>0.471</v>
       </c>
       <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5kg-yoggies-minigranule-iberico-veprove-maso-s-jablky-lisovane-za-studena-s-probiotiky</t>
+          <t>sodapup-honey-bone-odolna-nylonova-zvykaci-hracka-m</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5 kg Yoggies Ibérico vepřové maso s jablky, MINIgranule lisované za studena s probiotiky</t>
+          <t>SodaPup Honey bone, stevig nylon kauwspeeltje M</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Yoggies Ibérico varkensvlees met appels, koudgeperste korrels met probiotica</t>
+          <t>Flower´s Bone</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/iberico-met-appels-hypoallergeen</t>
+          <t>https://doglife.be/product/flowers-bone</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>37,10</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0.516</v>
+        <v>0.469</v>
       </c>
       <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2kg-yoggies-minigranule-iberico-veprove-maso-s-jablky-lisovane-za-studena-s-probiotiky</t>
+          <t>sodapup-mod-bone-odolna-zvykaci-hracka-l-19-1-x-4-4-cm</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2 kg Yoggies Ibérico vepřové maso s jablky, MINIgranule lisované za studena s probiotiky</t>
+          <t>SodaPup MOD bone, stevig kauwspeeltje, L 19,1 x 4,4 cm</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Yoggies Ibérico varkensvlees met appels, koudgeperste korrels met probiotica</t>
+          <t>Flower´s Bone</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/iberico-met-appels-hypoallergeen</t>
+          <t>https://doglife.be/product/flowers-bone</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>37,10</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0.516</v>
+        <v>0.469</v>
       </c>
       <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>roztok-na-cisteni-usi-senzi-auris-pro-psy-a-kocky-100-ml</t>
+          <t>sodapup-honey-bone-super-odolna-nylonovy-zvykaci-hracka-pro-psy-s</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Roztok na čištění uší SENZI-AURIS pro psy a kočky 100 ml</t>
+          <t>SodaPup Honey bone, stevig nylon kauwspeeltje, small</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Yoggies Chlorella voor honden 100g</t>
+          <t>Flower´s Bone</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/chlorella</t>
+          <t>https://doglife.be/product/flowers-bone</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>8,70</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.515</v>
+        <v>0.469</v>
       </c>
       <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tekuty-vosk-felleol-pro-upravu-srsti-psu-kocek-koni-100-ml</t>
+          <t>sodapup-honey-bone-odolna-nylonova-zvykaci-hracka-15-9-x-4-1-cm</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tekutý vosk FELLEOL pro úpravu srsti psů a koček 100 ml</t>
+          <t>SodaPup Honey bone, stevig nylon kauwspeeltje, large</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Yoggies Chlorella voor honden 100g</t>
+          <t>Flower´s Bone</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/chlorella</t>
+          <t>https://doglife.be/product/flowers-bone</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>8,70</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0.515</v>
+        <v>0.469</v>
       </c>
       <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>100g-verm-x-pamlsek-a-prirodni-prostredek-na-pravidelne-bezchemicke-odcerveni-psa</t>
+          <t>sodapup-fish-bone-super-odolna-nylonova-zvykaci-hracka-pro-psy</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>100 g, Verm-X, pamlsek a přírodní prostředek na podporu "bez chemického" odčervení psa</t>
+          <t>SodaPup Fish Bone, supersterk nylon kauwspeeltje voor honden</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Yoggies Chlorella voor honden 100g</t>
+          <t>Flower´s Bone</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/chlorella</t>
+          <t>https://doglife.be/product/flowers-bone</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>8,70</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.515</v>
+        <v>0.469</v>
       </c>
       <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tabletky-luposan-biotin-pro-psy-i-kocky-na-zdrave-drapy-srst-i-kuzi-180g-200ks</t>
+          <t>dogbar-xl</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tabletky Luposan Biotin+ pro psy i kočky na zdravé drápy, srst i kůži, 180 g/200 ks</t>
+          <t>DogBar XL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Yoggies kelp – zeewier- voor honden en katten 180g</t>
+          <t>Bijtkussen RINGO, 3 oren, XL, 28×15 h7 cm, ORANJA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/kelp-zeewier-voor-honden-en-katten</t>
+          <t>https://doglife.be/product/bijtkussen-ringo-3-oren-xl-28x15-h7-cm-oranja</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>9,60</t>
+          <t>25,20</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0.514</v>
+        <v>0.465</v>
       </c>
       <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5-1-yoggies-drubezi-konzerva-se-zeleninou-a-ovesnymi-vlockami-200g</t>
+          <t>soda-pup-senzoricka-miska-rocni-obdobi</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5+1 Yoggies drůbeží konzerva se zeleninou a ovesnými vločkami 200 g</t>
+          <t>SodaPup Vier jaargetijden, sensorische kom - groen</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>200g Yoggies blik Kangoeroe met pompoen</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/200g-yoggies-blik-kangoeroe-met-pompoen</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2,10</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.501</v>
+        <v>0.464</v>
       </c>
       <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>200g-yoggies-drubezi-konzerva-s-ovesnymi-vlockami</t>
+          <t>10kg-yoggies-vet-gastro-sensitive-s-krutim-masem-minigranule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>200 g Yoggies drůbeží konzerva se zeleninou a ovesnými vločkami</t>
+          <t>10 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>200g Yoggies blik Kangoeroe met pompoen</t>
+          <t>Yoggies Kalkoen met Gierst, koudgeperste MINI korrels met probiotica</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/200g-yoggies-blik-kangoeroe-met-pompoen</t>
+          <t>https://doglife.be/product/hypoalergeen-kalkoenvlees-met-gierst-en-hennepolie-mini</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2,10</t>
+          <t>15,00</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0.501</v>
+        <v>0.46</v>
       </c>
       <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>700g-b-a-r-f-losos-a-kralik-s-probiotiky</t>
+          <t>vzorky-granuli-yoggies-vet-pro-psy-velikost-mini-balicek-vzorku-3-druhu-granuli</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>700 g B.A.R.F. Losos a králík s probiotiky</t>
+          <t>Proefmonster Yoggies VET brokken voor honden - maat MINI</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>700 g Yoggies BARF 100% kalkoen met probiotica Rauw vlees voor honden</t>
+          <t>2 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste  MINI korrels met probiotica</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/700-g-yoggies-barf-100-kalkoen-met-probiotica-rauw-vlees-voor-honden</t>
+          <t>https://doglife.be/product/2-kg-yoggies-vet-gastro-sensitive-met-kalkoenvlees-koudgeperste-mini-korrels-met-probiotica</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>4,30</t>
+          <t>19,70</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.496</v>
+        <v>0.459</v>
       </c>
       <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>yoggies-konzerva-kozi-s-bramborem-a-mrkvi</t>
+          <t>yoggies-ekologicke-stelivo-pro-kocky-6-x-3-kg</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Yoggies konzerva Kozí s bramborem a mrkví</t>
+          <t>Yoggies ecologische kattenbakvulling 6 x 3 kg</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>800g Yoggies blik geit met aardappelen en wortelen</t>
+          <t>Ultimate Litter Mat – Ultieme kattenbakmat 90 x 60</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/yoggies-geit-met-aardappelen-en-wortelen-800-g</t>
+          <t>https://doglife.be/product/ultimate-litter-mat-ultieme-kattenbakmat-90-x-60</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>5,30</t>
+          <t>24,40</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.494</v>
+        <v>0.448</v>
       </c>
       <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>250ml-lupoderm-olej-a-doplnek-potravy-pro-zdravou-kuzi-a-srst</t>
+          <t>200g-yoggies-jehneci-konzerva-s-bramborem-a-karotkou</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>250 ml, LupoDerm - olej a doplněk potravy pro zdravou kůži a srst</t>
+          <t>200 g Yoggies lam blikvoer met aardappel en wortel</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LUPO Premium Wildfish Oil 250 ml</t>
+          <t>200g Yoggies blik lam met aardappelen en wortelen</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/lupo-premium-wildfish-oil-250-ml</t>
+          <t>https://doglife.be/product/yoggies-blik-lam-met-aarappelen-en-wortelen-200-g</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>20,90</t>
+          <t>1,50</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0.48</v>
+        <v>0.448</v>
       </c>
       <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>termokrabice-na-b-a-r-f</t>
+          <t>5-1-yoggies-jehneci-konzerva-s-bramborem-a-karotkou-400g</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mrazicí box</t>
+          <t>5+1 Yoggies lam blikvoer met aardappel en wortel 400 g</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BRAVO – Deluxe Tin Box Twisted Sticks (1,8 x 12.5 cm) 790 g</t>
+          <t>400g Yoggies blik lam met aardappelen en wortelen</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/bravo-deluxe-tin-box-twisted-sticks-18-x-12-5-cm-790-g</t>
+          <t>https://doglife.be/product/yoggies-lamsvlees-in-blik-met-aardappelen-en-wortelen-400-g</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0.473</v>
+        <v>0.448</v>
       </c>
       <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>yoggies-balicek-na-cestu-active-kachni</t>
+          <t>5-1-yoggies-jehneci-konzerva-s-bramborem-a-karotkou-200g</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Yoggies balíček na cestu pro štěně - Active kachní</t>
+          <t>5+1 Yoggies lam blikvoer met aardappel en wortel 200 g</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LIZA 400g Eend</t>
+          <t>200g Yoggies blik lam met aardappelen en wortelen</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/liza-400g-eend</t>
+          <t>https://doglife.be/product/yoggies-blik-lam-met-aarappelen-en-wortelen-200-g</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2,00</t>
+          <t>1,50</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0.472</v>
+        <v>0.448</v>
       </c>
       <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sodapup-honey-bone-odolna-nylonova-zvykaci-hracka-m</t>
+          <t>400g-yoggies-jehneci-konzerva-s-bramborem-a-karotkou</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SodaPup Honey bone, odolná nylonová žvýkací hračka M</t>
+          <t>400 g Yoggies lam blikvoer met aardappel en wortel</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Flower´s Bone</t>
+          <t>400g Yoggies blik lam met aardappelen en wortelen</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/flowers-bone</t>
+          <t>https://doglife.be/product/yoggies-lamsvlees-in-blik-met-aardappelen-en-wortelen-400-g</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0.469</v>
+        <v>0.448</v>
       </c>
       <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sodapup-mod-bone-odolna-zvykaci-hracka-l-19-1-x-4-4-cm</t>
+          <t>10kg-yoggies-jehneci-maso-bila-ryba-minigranule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SodaPup MOD bone, odolná žvýkací hračka, L 19,1 x 4,4 cm</t>
+          <t>10 kg Yoggies lamsvlees &amp; witvis, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Flower´s Bone</t>
+          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/flowers-bone</t>
+          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>33,20</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.469</v>
+        <v>0.435</v>
       </c>
       <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>sodapup-honey-bone-super-odolna-nylonovy-zvykaci-hracka-pro-psy-s</t>
+          <t>10kg-yoggies-vet-insect-derma-s-hmyzim-proteinem-minigranule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SodaPup Honey bone, odolná nylonový žvýkací hračka, small</t>
+          <t>10 kg Yoggies VET Insect Derma met insectenproteïne, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Flower´s Bone</t>
+          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/flowers-bone</t>
+          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>33,20</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0.469</v>
+        <v>0.435</v>
       </c>
       <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>sodapup-honey-bone-odolna-nylonova-zvykaci-hracka-15-9-x-4-1-cm</t>
+          <t>10kg-yoggies-vet-veggie-bez-masa-minigranule-lisovane-za-studena-s-probiotiky</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SodaPup Honey bone, odolná nylonová žvýkací hračka, large</t>
+          <t>10 kg Yoggies VET Veggie vleesvrij, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Flower´s Bone</t>
+          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/flowers-bone</t>
+          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>33,20</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.469</v>
+        <v>0.435</v>
       </c>
       <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sodapup-fish-bone-super-odolna-nylonova-zvykaci-hracka-pro-psy</t>
+          <t>15kg-minigranule-yoggies-jehneci-a-bila-ryba-granule-lisovane-za-studena</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SodaPup Fish Bone, super odolná nylonová žvýkací hračka pro psy</t>
+          <t>15 kg Yoggies lamsvlees &amp; witvis, koudgeperste MINIbrokken met probiotica</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Flower´s Bone</t>
+          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/flowers-bone</t>
+          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>33,20</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.469</v>
+        <v>0.435</v>
       </c>
       <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2kg-yoggies-vet-veggie-bez-masa-minigranule-lisovane-za-studena-s-probiotiky</t>
+          <t>sodapup-lizaci-podlozka-love-mala-18-x-13cm-cervena</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2 kg Yoggies VET Veggie bez masa, MINIgranule lisované za studena s probiotiky</t>
+          <t>SodaPup likmat love klein, rood</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste  MINI korrels met probiotica</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/2-kg-yoggies-vet-gastro-sensitive-met-kalkoenvlees-koudgeperste-mini-korrels-met-probiotica</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>19,70</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0.469</v>
+        <v>0.424</v>
       </c>
       <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dogbar-xl</t>
+          <t>sodapup-lizaci-podlozka-s-prisavkami-velryba-modra</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DogBar XL</t>
+          <t>SodaPup likmat met zuignappen, Walvis – blauw</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bijtkussen RINGO, 3 oren, XL, 28×15 h7 cm, ORANJA</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/bijtkussen-ringo-3-oren-xl-28x15-h7-cm-oranja</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>25,20</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0.465</v>
+        <v>0.424</v>
       </c>
       <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5kg-yoggies-kozi-masozelenina-hypoalergenni-granule-lisovane-za-studena-s-probiotiky</t>
+          <t>sodapup-senzoricka-miska-slunecnice-zluta</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5 kg Yoggies Kozí maso &amp; zelenina, hypoalergenní granule lisované za studena s probiotiky</t>
+          <t>SodaPup sensorische kom - Zonnebloem, geel</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>5 kg Yoggies VET Gastro Sensitive met kalkoen, koudgeperste korrels met probiotica</t>
+          <t>LIKMAT – SodaPup Mandala Nylon Zintuiglijke Kom – Groen</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://doglife.be/product/vet-gastro-sensitive-met-kalkoen-en-probiotica-5-kg</t>
+          <t>https://doglife.be/product/likmat-sodapup-mandala-nylon-zintuiglijke-kom-groen</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>49,40</t>
+          <t>21,30</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0.464</v>
+        <v>0.423</v>
       </c>
       <c r="G112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>5-kg-jehneci-a-bila-ryba-granule-lisovane-za-studena-s-probiotiky-yoggies</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>5 kg Yoggies Jehněčí maso &amp; bílá ryba, granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>5 kg Yoggies VET Gastro Sensitive met kalkoen, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/vet-gastro-sensitive-met-kalkoen-en-probiotica-5-kg</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>49,40</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="G113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>10kg-yoggies-jehneci-maso-bila-ryba-granule-lisovane-za-studena-s-probiotiky</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>10 kg Yoggies Jehněčí maso &amp; bílá ryba, granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Yoggies Lam en Witte Vis, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/lam-en-witte-vis</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>36,80</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>20kg-jehneci-a-bila-ryba-granule-lisovane-za-studena-yoggies</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>20 kg Yoggies Jehněčí maso &amp; bílá ryba, granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Yoggies Lam en Witte Vis, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/lam-en-witte-vis</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>36,80</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2kg-jehneci-a-bila-ryba-granule-lisovane-za-studena-s-probiotiky-yoggies</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2 kg Yoggies Jehněčí maso &amp; bílá ryba, granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Yoggies Lam en Witte Vis, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/lam-en-witte-vis</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>36,80</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>15kg-jehneci-a-bila-ryba-granule-lisovane-za-studena-yoggies</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>15 kg Yoggies Jehněčí maso &amp; bílá ryba, granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Yoggies Lam en Witte Vis, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/lam-en-witte-vis</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>36,80</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2kg-hypoalergenni-granule-yoggies-s-kozim-masem-a-br-vlockami-lisovane-za-studena-s-probiotiky</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2 kg Yoggies Kozí maso &amp; zelenina, hypoalergenní granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2kg Yoggies BARF+ MINI bijgerecht voor rauw vlees, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/barfmini-volledig-vleesloos-gerecht-aan-b-a-r-f-2-kg</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>14,40</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="G118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>5-kg-minigranule-monoproteinove-yoggies-s-krutim-masem-a-jahly-lisovane-za-studena-s-probiotiky</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>5 kg Yoggies Krůtí maso &amp; jáhly, MINIgranule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>5 kg Yoggies VET Gastro Sensitive met kalkoen, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/vet-gastro-sensitive-met-kalkoen-en-probiotica-5-kg</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>49,40</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="G119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2kg-minigranule-monoproteinove-yoggies-s-krutim-masem-a-jahly-lisovane-za-studena-s-probiotiky</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2 kg Yoggies Krůtí maso &amp; jáhly, MINIgranule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2 kg Yoggies VET Gastro Sensitive met kalkoenvlees, koudgeperste  MINI korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/2-kg-yoggies-vet-gastro-sensitive-met-kalkoenvlees-koudgeperste-mini-korrels-met-probiotica</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>19,70</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="G120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>10kg-yoggies-kozi-maso-zelenina-hypoalergenni-granule-lisovane-za-studena-s-probiotiky</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>10 kg Yoggies Kozí maso &amp; zelenina, hypoalergenní granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>33,20</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>10kg-yoggies-vet-insect-derma-s-hmyzim-proteinem-granule-lisovane-za-studena-s-probiotiky</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>10 kg Yoggies VET Insect Derma s hmyzím proteinem, granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>33,20</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="G122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>10kg-yoggies-vet-gastro-sensitive-s-krutim-masem-granule-lisovane-za-studena-s-probiotiky</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>10 kg Yoggies VET Gastro Sensitive s krůtím masem, granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>33,20</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>20kg-hypoalergenni-granule-yoggies-s-kozim-masem-a-br-vlockami-lisovane-za-studena</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>20 kg Yoggies Kozí maso &amp; zelenina, hypoalergenní granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>33,20</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>10kg-yoggies-vet-veggie-bez-masa-granule-lisovane-za-studena-s-probiotiky</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>10 kg Yoggies VET Veggie bez masa, granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>33,20</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="G125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>15kg-hypoalergenni-granule-yoggies-s-kozim-masem-a-br-vlockami-lisovane-za-studena</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>15 kg Yoggies Kozí maso &amp; zelenina, hypoalergenní granule lisované za studena s probiotiky</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Yoggies Kip en Rund, koudgeperste korrels met probiotica</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/kip-en-rund-klassiek</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>33,20</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="G126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>yoggies-balicek-na-cestu-pro-stene-kureci</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Yoggies balíček na cestu pro štěně - Kuřecí &amp; hovězí</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>120g Yoggies paté – kip</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/pate-voor-honden-kip</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>5,40</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="G127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>150g-yoggies-varena-potrava-pro-psy-kureci-maso-s-ryzi</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>150 g Yoggies Vařená potrava pro psy – kuřecí maso s rýží</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Freedog Parfums voor honden en katten 150 ml</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/freedog-parfums-voor-honden-en-katten-150-ml</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>16,20</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="G128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>150g-yoggies-varena-potrava-pro-psy-veprove-maso-s-ryzi</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>150 g Yoggies Vařená potrava pro psy – vepřové maso s rýží</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Freedog Parfums voor honden en katten 150 ml</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/freedog-parfums-voor-honden-en-katten-150-ml</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>16,20</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="G129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>yoggies-varena-potrava-pro-psy-kruti-a-kralici-maso-s-dynovymi-seminky-a-kloubni-vyzivou</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>150 g Yoggies Vařená potrava pro psy – krůtí a králičí maso s dýňovými semínky</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Freedog Parfums voor honden en katten 150 ml</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/freedog-parfums-voor-honden-en-katten-150-ml</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>16,20</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>150g-yoggies-varena-potrava-pro-psy-kruti-maso-s-pohankou-a-kloubni-vyzivou</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>150 g Yoggies Vařená potrava pro psy – krůtí maso s pohankou</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Freedog Parfums voor honden en katten 150 ml</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/freedog-parfums-voor-honden-en-katten-150-ml</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>16,20</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="G131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>150g-yoggies-varena-potrava-pro-psy-hovezi-maso-s-quinoou-a-kloubni-vyzivou</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>150 g Yoggies Vařená potrava pro psy – hovězí maso s quinoou</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Freedog Parfums voor honden en katten 150 ml</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>https://doglife.be/product/freedog-parfums-voor-honden-en-katten-150-ml</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>16,20</t>
-        </is>
-      </c>
-      <c r="F132" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="G132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
